--- a/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0014.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/lore/lang_multi_text/lang_multi_text__lore__part_0014.xlsx
@@ -595,19 +595,19 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>Nàng tỉnh giấc sau giấc mơ.
-Mặt trời vừa ló dạng trên đường chân trời, phủ lên &lt;te href=850109&gt;Black Shores&lt;/te&gt; một ánh sáng ấm áp. Một ngày mới lại bắt đầu, bình thường như bao ngày khác. Camellya mở mắt, duỗi người một cách thong thả trên ngọn cây. Động tác của nàng uyển chuyển đến mức việc té ngã dường như là điều không thể. Dù có trượt chân, những dây leo cũng sẽ đỡ lấy nàng. Nàng thích ngủ như thế này, tránh xa mọi sự ồn ào và con người.
+Mặt trời vừa ló dạng trên đường chân trời, phủ lên &lt;te href=850109&gt;Bờ Biển Đen&lt;/te&gt; một ánh sáng ấm áp. Một ngày mới lại bắt đầu, bình thường như bao ngày khác. Camellya mở mắt, duỗi người một cách thong thả trên ngọn cây. Động tác của nàng uyển chuyển đến mức việc té ngã dường như là điều không thể. Dù có trượt chân, những dây leo cũng sẽ đỡ lấy nàng. Nàng thích ngủ như thế này, tránh xa mọi sự ồn ào và con người.
 "Sáng đẹp làm sao," nàng thầm nghĩ. Tâm trí và thể xác đều vững vàng, ý nghĩ về việc phải dùng đến buồng y tế dường như rất xa vời. Đó là điều tốt.
-Nàng biết {PlayerName} sẽ ở lại Black Shores, chuẩn bị cho {Male=chuyến hành trình;Female=chuyến hành trình} tới &lt;te href=850096&gt;Rinascita&lt;/te&gt;. Điều đó khiến nàng vui mừng, vì có nghĩa là sẽ có thêm thời gian để trò chuyện, cười đùa và ở bên nhau.
+Nàng biết {PlayerName} sẽ ở lại Bờ Biển Đen, chuẩn bị cho {Male=him;Female=her} tới &lt;te href=850096&gt;Rinascita&lt;/te&gt;. Điều đó khiến nàng vui mừng, vì có nghĩa là sẽ có thêm thời gian để trò chuyện, cười đùa và ở bên nhau.
 Nàng đã tặng {PlayerName} một món quà, một chiếc vòng tay theo dõi tần số, giống như chiếc mà {Male=chàng;Female=nàng} đã tặng nàng trước đây.
 Đó là món quà đầu tiên nàng từng chuẩn bị cho ai đó.
 "Thật kỳ lạ!" nàng tự nhủ. Lo lắng cho sự an toàn của ai đó, hay thậm chí là liệu họ có thật sự tồn tại... đó quả là một cảm giác mới mẻ! Chắc hẳn điều đó có nghĩa là nàng quan tâm đến cuộc sống của họ. Những suy nghĩ như vậy thật xa lạ—nàng chưa bao giờ bận tâm đến sinh mạng của chính mình, hay của bất kỳ ai khác. Nhưng sau khi rời khỏi Ma Trận Sao cùng {PlayerName} và khám phá ra thân phận thật của mình là Quý Nữ Flora, nàng đã bắt đầu nhìn mọi thứ dưới một góc độ mới mẻ, dù chỉ là rất nhỏ.
 Dù vậy, nàng không có ý định theo {PlayerName} đến Rinascita. Quan điểm của họ về một số khía cạnh lịch sử của &lt;te href=850079&gt;Solaris&lt;/te&gt; khác nhau, và cũng như nàng không định can thiệp vào {Male=lựa chọn;Female=lựa chọn} của {PlayerName}, nàng cũng không cảm thấy cần phải giải thích cho {Male=chàng;Female=nàng} về lý do của mình. Thực tế, để tránh gánh nặng cho {PlayerName}, nàng đã giấu đi một số sự thật. Trong Ma Trận Sao, nàng không hề mất hết ký ức về quá khứ của mình.
 Đúng vậy, quá khứ của nàng... Camellya nheo mắt, một tiếng ngân nhẹ thoát ra khỏi môi khi nàng suy nghĩ về bước đi tiếp theo. Nàng muốn tự mình điều tra thêm, chờ đợi thời điểm thích hợp để chia sẻ những gì mình biết với {PlayerName}. Nàng không tin tưởng vào tổ chức được xây dựng trên bờ biển này, và càng không tin vào &lt;te href=850110&gt;Hệ thống Tethys&lt;/te&gt;. Ngoài {PlayerName} ra, nàng không tin ai khác.
-Từng có thời, với tư cách là Quý Nữ Flora, nàng Dodge mọi ràng buộc, không muốn chứng kiến {PlayerName} hy sinh {Male=bản thân;Female=bản thân} vì lợi ích chung. Nhưng giờ đây, quan điểm của nàng đã thay đổi. Nàng thấy mình ít giống Quý Nữ Flora của quá khứ.
+Từng có thời, với tư cách là Quý Nữ Flora, nàng né tránh mọi ràng buộc, không muốn chứng kiến {PlayerName} hy sinh {Male=bản thân;Female=bản thân} vì lợi ích chung. Nhưng giờ đây, quan điểm của nàng đã thay đổi. Nàng thấy mình ít giống Quý Nữ Flora của quá khứ.
 Nàng đã theo dõi hành trình của {PlayerName} từ &lt;te href=850091&gt;Jinzhou&lt;/te&gt; cho đến giờ.
 Một sức mạnh đơn độc, luôn tiến về phía trước, thu thập những người bạn đồng hành đa dạng trên đường đi.
 Nàng hiểu rằng đây vẫn chưa phải là con đường của mình, nhưng nàng không còn chống lại việc quan sát nó nữa. Giống như một viên sỏi gặp một viên sỏi khác, tạo ra những gợn sóng trên mặt nước, nàng chấp nhận trở thành một "biến số" trong vũ điệu này. Giờ đây, niềm vui mà nàng cảm nhận từ mối liên kết với {PlayerName} thật sâu sắc. Nàng không còn cảm thấy sự nhàm chán thường thấy, cũng không muốn xóa bỏ những suy nghĩ về {Male=chàng;Female=nàng}. Thay vào đó, tâm trí nàng thường hướng về {Male=chàng;Female=nàng}, khao khát được biết thêm về {Male=những cuộc phiêu lưu;Female=những cuộc phiêu lưu} của {PlayerName} và chia sẻ thêm những trò chơi thú vị. Chính lúc đó, Camellya nhận ra rằng những suy nghĩ ấy đã để lại những vết hằn vừa đau đớn vừa ngọt ngào trong tâm hồn nàng, từ rất lâu trước khi nàng kịp nhận ra.
-Bỗng nhiên cảm hứng tràn về, nàng kích hoạt Terminal và soạn một tin nhắn ngắn gửi cho {PlayerName}, dự định sẽ gửi đi ngay trước khi {Male=chàng;Female=nàng} lên đường. Chiếc vòng tay cho phép nàng kiểm tra tình trạng của {PlayerName} bất cứ lúc nào, nên không có gì phải lo lắng. Dù Solaris rộng lớn, nàng tin rằng nếu họ là những sợi chỉ trong cùng một câu chuyện, đường đi của họ chắc chắn sẽ giao nhau.
+Bỗng nhiên cảm hứng tràn về, nàng kích hoạt Thiết bị đầu cuối và soạn một tin nhắn ngắn gửi cho {PlayerName}, dự định sẽ gửi đi ngay trước khi {Male=chàng;Female=nàng} lên đường. Chiếc vòng tay cho phép nàng kiểm tra tình trạng của {PlayerName} bất cứ lúc nào, nên không có gì phải lo lắng. Dù Solaris rộng lớn, nàng tin rằng nếu họ là những sợi chỉ trong cùng một câu chuyện, đường đi của họ chắc chắn sẽ giao nhau.
 Vào thời điểm {PlayerName} còn chưa hay biết gì, đó chính là lúc nàng sẽ khiến {Male=chàng;Female=nàng} bất ngờ!
 Khi tưởng tượng đến khoảnh khắc đáng yêu ấy, một giai điệu thoát ra khỏi môi nàng. Những dây leo quấn quanh cánh tay, vươn lên trên, những nụ hoa nhỏ bắt đầu hé nở ở đầu ngọn.
 Bỗng nhiên, một ý nghĩ lóe lên trong đầu nàng.
@@ -711,8 +711,8 @@
 Lẩm bẩm một mình, Quý cô Flora bĩu môi rồi đẩy cửa xe ra. "Thôi được, tôi đi tìm anh ấy đây!"
 Người Mang Hoa vẫy tay tiễn nàng, rõ ràng đã quen với động thái này giữa Flora và thủ lĩnh của họ.
 Rời khỏi sự ấm áp của xe, Flora lê bước trên lớp tuyết dày, ký ức về lần gặp đầu tiên ở Làng Petalfall ùa về. Nàng biết họ sẽ đến vùng đồng bằng tuyết này vì nhiệm vụ, và dù không ưa cái lạnh, nàng vẫn tin rằng khoảng thời gian bên thủ lĩnh của &lt;te href=850109&gt;Bờ Đen&lt;/te&gt; sẽ đáng giá. Hầu hết thời gian, nàng chọn đồng hành cùng {PlayerName} trong các chuyến đi, để lại dấu chân trên khắp &lt;te href=850079&gt;Solaris&lt;/te&gt;, từ những thị trấn nhộn nhịp đến những ngóc ngách bí ẩn, từ nơi trú ẩn an toàn đến vùng đất nguy hiểm. Flora yêu thích cuộc sống này, tràn đầy cảm giác phiêu lưu, và {PlayerName} có tài biến những điều bình thường thành điều phi thường.
-Nàng không ngại nguy hiểm. Thực ra, nàng còn thích nó nữa. Với nàng, nguy hiểm đồng nghĩa với thay đổi, và thay đổi dẫn đến hứng thú. Nhưng khi ở bên thủ lĩnh, nàng lại kìm Dodgen bản năng tìm kiếm rắc rối để vui đùa.
-Danger...
+Nàng không ngại nguy hiểm. Thực ra, nàng còn thích nó nữa. Với nàng, nguy hiểm đồng nghĩa với thay đổi, và thay đổi dẫn đến hứng thú. Nhưng khi ở bên thủ lĩnh, nàng lại kìm nén bản năng tìm kiếm rắc rối để vui đùa.
+Nguy hiểm...
 Camellya giơ tay lên, sợi dây chuyền mảnh mai trên cổ tay lấp lánh dưới ánh sáng. Vòng đeo tay theo dõi chỉ số Rabelle của nàng vẫn bình thường. Nàng siết nhẹ cổ tay và thở ra nhẹ nhõm. "Tốt, mọi thứ vẫn ổn," nàng nghĩ. "Nếu mình mất kiểm soát, anh ấy sẽ phải lo cho mình. Như vậy sẽ ảnh hưởng đến cả nhiệm vụ."
 Nàng ghét mất kiểm soát.
 Những năm gần đây, Flora thường bị ám ảnh bởi những giấc mơ kỳ lạ và rời rạc. Chúng giống như ký ức của một cuộc đời mà nàng chưa từng sống. Trong những giấc mơ đó, nàng luôn tìm kiếm {PlayerName}, nhưng hai người không bao giờ gặp được nhau. Mỗi lần tỉnh giấc, một nỗi bất an tràn ngập tâm trí, khiến nàng phải đến cơ sở y tế của Bờ Đen.
@@ -797,18 +797,18 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Trong căn phòng tím mờ ảo, những giọng nói hòa quyện vào nhau—vừa uy nghi và mê hoặc, vừa lạnh lẽo và kiên định, lại vừa chân thành và ngây thơ. Chúng đan xen, tạo nên một bản giao hưởng mơ màng. Ánh sáng ngọc bích lấp lánh với uy quyền tĩnh lặng, những trang sách xào xạc khẽ khàng, và hương thơm của bánh nướng mới ra lò hòa quyện cùng hơi ấm của căn phòng, tạo nên một bầu không khí ngọt ngào, siêu thực.
-Cantarella nhấc chiếc ấm trà tinh xảo lên và rót trà, một sự thay đổi so với thường lệ. Không còn là sắc tím quyến rũ, mà là một tách trà trong veo, tươi mát.
-"Cảm ơn những ý kiến quý báu của các bạn," cô nói, đặt ấm trà xuống. Hương thơm tươi mới lan tỏa khắp phòng. "Giờ thì, tôi đã quyết định."
-"Tôi sẽ tiếp tục đội chiếc vương miện gai, vì nọc độc đã ngấm sâu vào xương tủy tôi, và giấc mơ là một phần của tôi mà tôi không thể loại bỏ."
+          <t>Trong căn phòng tím mờ ảo, những giọng nói hòa quyện vào nhau—vừa uy nghiêm mê hoặc, vừa lạnh lùng kiên định, lại vừa chân thành ngây thơ. Chúng đan xen, tạo nên một bản giao hưởng mơ hồ. Ánh sáng ngọc bích lấp lánh với uy quyền tĩnh lặng, những trang sách xào xạc nhẹ nhàng, và hương thơm của bánh nướng mới hòa quyện cùng hơi ấm căn phòng, tạo nên một không gian ngọt ngào, siêu thực.
+Cantarella nhấc chiếc ấm trà tinh xảo lên và rót trà, một sự thay đổi so với thường lệ. Không còn sắc tím quyến rũ, mà là một tách trà trong veo, tươi mát.
+"Cảm ơn các bạn vì những ý kiến quý báu," cô nói, đặt ấm trà xuống. Hương thơm tươi mới lan tỏa khắp phòng. "Giờ thì, tôi đã quyết định rồi."
+"Tôi sẽ tiếp tục đội chiếc vương miện gai, vì nọc độc đã ngấm sâu vào xương tủy, và giấc mơ đã là một phần không thể tách rời của tôi."
 "Tôi sẽ tiếp tục pha chế những lọ thuốc, vì chúng không chỉ cần thiết cho &lt;te href=850094&gt;Fisalias&lt;/te&gt;, mà còn cho tất cả những ai đang đấu tranh."
-"Tôi sẽ bước ra ngoài và đi theo đàn chim bay, vào núi non và phố phường. Những lời thì thầm từng giam cầm chúng ta đã biến mất, và giờ đây chúng ta được tự do."
-"Tôi vẫn còn ở trong giấc mơ, nhưng tôi sẽ cố gắng cảm nhận mặt đất dưới chân mình… Trong khoảnh khắc thoáng qua giữa giấc mơ và thực tại, tôi sẽ níu giữ những gì là thật."
-Cantarella hít một hơi thật sâu, từ từ mở mắt. Cô vừa tỉnh dậy sau một giấc ngủ trưa ngắn ngủi, bước ra từ một giấc mơ mờ ảo nhưng lại rõ ràng đến kỳ lạ. Ánh nắng lúc ba giờ chiều lọt qua khung cửa kính, phủ lên hình dáng cô đơn của cô trong căn phòng một ánh sáng dịu êm. Những âm thanh duy nhất còn lại là tiếng trà sủi bọt nhẹ nhàng và hơi thở đều đặn của cô.
-Cô nhấc tách trà lên và nhấp một ngụm. Hương thơm tươi mát xoa dịu &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; bất an trong miệng cô. Nó không còn hút năng lượng từ ảo giác hay đau đớn nữa. Đây là loại trà cô đã mua sáng nay ở &lt;te href=850097&gt;Ragunna&lt;/te&gt;, chỉ là trà bình thường. Vị ngọt nhẹ và hương thơm thoang thoảng gợi nhớ về làn gió ở miền quê, về những giọt sương đọng trên lá non…
-Vậy đấy, đây chính là hương vị của bình yên và hạnh phúc sau khi mọi chuyện đã lắng dịu.
-Cánh cửa kẽo kẹt mở ra. Cô rót thêm một tách trà và mời vị khách vừa bước vào. Vị khách có mái tóc đen và đôi mắt vàng, mang đến sự điềm tĩnh và sức mạnh vững chãi, neo giữ căn phòng. Buổi chiều yên ả và tĩnh lặng này là một phép màu mà không ai khác ngoài {PlayerName} có thể mang lại.
-Ánh nắng dịu dàng lướt qua căn phòng, và hương thơm tươi mát vương vấn giữa họ, tràn ngập không gian quanh hai tách trà. Cô ngước đôi mắt tím xanh lên, làn sương mù đã tan biến từ lâu, ánh nhìn giờ đây như mặt biển lặng, chỉ còn những gợn sóng nhẹ nhàng của cảm xúc.</t>
+"Tôi sẽ bước ra ngoài, theo dấu cánh chim bay vào núi rừng và phố thị. Những lời thì thầm từng giam cầm chúng ta đã biến mất, giờ đây chúng ta được tự do."
+"Tôi vẫn còn trong giấc mơ, nhưng tôi sẽ cố gắng cảm nhận mặt đất dưới chân mình… Trong khoảnh khắc thoáng qua giữa mơ và thực, tôi sẽ níu giữ những gì chân thật."
+Cantarella hít một hơi thật sâu, từ từ mở mắt. Cô vừa tỉnh dậy sau một giấc ngủ trưa ngắn ngủi, bước ra từ một giấc mơ mờ ảo nhưng lại rõ ràng đến lạ lùng. Ánh nắng lúc ba giờ chiều xuyên qua khung cửa kính, phủ lên thân hình cô một vệt sáng tĩnh lặng trong căn phòng. Những âm thanh duy nhất còn lại là tiếng trà sôi lăn tăn và nhịp thở đều đặn của cô.
+Cô nhấc tách lên và nhấp một ngụm. Hương thơm tươi mát xoa dịu vết &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; bất an trong miệng cô. Nó không còn hút lấy sức mạnh từ ảo ảnh hay đau đớn nữa. Đây là loại trà cô mua sáng nay ở &lt;te href=850097&gt;Ragunna&gt;, chỉ là trà bình thường thôi. Vị ngọt nhẹ và hương thơm thoang thoảng gợi nhớ về làn gió quê nhà, về những giọt sương đọng trên lá non…
+Vậy ra đây là hương vị của bình yên và hạnh phúc sau khi mọi thứ đã lắng xuống.
+Cánh cửa kẽo kẹt mở ra. Cô rót thêm một tách nữa và mời vị khách vừa bước vào. Vị khách có mái tóc đen và đôi mắt vàng, mang đến sự điềm tĩnh và sức mạnh vững chãi cho căn phòng. Buổi chiều yên ả và thanh bình này là món quà kỳ diệu mà chỉ có {PlayerName} mới mang lại được.
+Ánh nắng dịu nhẹ lướt qua căn phòng, hương thơm tươi mát vương vấn giữa họ, tràn ngập không gian quanh hai tách trà. Cô ngước đôi mắt tím xanh lên, làn sương mù đã tan biến từ lâu, ánh nhìn giờ đây như mặt biển lặng, chỉ còn những gợn sóng cảm xúc nhẹ nhàng.</t>
         </is>
       </c>
     </row>
@@ -15634,7 +15634,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Dù vùng biên giới không thể sánh với sự náo nhiệt và hào nhoáng của thành phố, nhưng nơi đây vẫn có Dodget quyến rũ riêng. Nếu có thời gian, ta khuyên cậu nên đến chiêm ngưỡng trăng tròn và những vì sao lấp lánh trên bầu trời đêm yên bình. Đừng lo về an toàn, ta sẽ ở đó cùng cậu.</t>
+          <t>Dù vùng biên giới không thể sánh với sự náo nhiệt và hào nhoáng của thành phố, nhưng nơi đây vẫn có nét quyến rũ riêng. Nếu có thời gian, ta khuyên cậu nên đến chiêm ngưỡng trăng tròn và những vì sao lấp lánh trên bầu trời đêm yên bình. Đừng lo về an toàn, ta sẽ ở đó cùng cậu.</t>
         </is>
       </c>
     </row>
@@ -24023,7 +24023,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Tên khoa học "Resinacrustidum lapis", thuộc loài Resinacrustidum. Discord này thường hoạt động theo đàn trong các khu mỏ và vùng núi, cùng với Fission Junrocks. Ít nguy hiểm hơn.</t>
+          <t>Tên khoa học "Resinacrustidum lapis", thuộc loài Resinacrustidum. Tacet Discord này thường hoạt động theo đàn trong các khu mỏ và vùng núi, cùng với Fission Junrocks. Ít nguy hiểm hơn.</t>
         </is>
       </c>
     </row>
@@ -24218,7 +24218,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Cái tên "Exile" đồng nghĩa với trọng tội không thể tha thứ. Những kẻ bị lưu đày không được phép đặt chân vào thị trấn, buộc phải lang thang nơi hoang dã. Dù đa số chỉ đang trả giá cho những lỗi lầm trong quá khứ, nhưng xét rằng các phiên tòa không phải lúc nào cũng "công bằng" ở mọi quốc gia, không ít kẻ lưu đày bị trục xuất oan uổng và ôm hận trong lòng.</t>
+          <t>Cái tên "Kẻ Lưu Đày" đồng nghĩa với trọng tội không thể tha thứ. Những kẻ bị lưu đày không được phép đặt chân vào thị trấn, buộc phải lang thang nơi hoang dã. Dù đa số chỉ đang trả giá cho những lỗi lầm trong quá khứ, nhưng xét rằng các phiên tòa không phải lúc nào cũng "công bằng" ở mọi quốc gia, không ít kẻ lưu đày bị trục xuất oan uổng và ôm hận trong lòng.</t>
         </is>
       </c>
     </row>
@@ -24283,7 +24283,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Cái tên "Exile" đồng nghĩa với trọng tội không thể tha thứ. Những kẻ bị lưu đày không được phép đặt chân vào thị trấn, buộc phải lang thang nơi hoang dã. Dù đa số chỉ đang trả giá cho những lỗi lầm trong quá khứ, nhưng xét rằng các phiên tòa không phải lúc nào cũng "công bằng" ở mọi quốc gia, không ít kẻ lưu đày bị trục xuất oan uổng và ôm hận trong lòng.</t>
+          <t>Cái tên "Kẻ Lưu Đày" đồng nghĩa với trọng tội không thể tha thứ. Những kẻ bị lưu đày không được phép đặt chân vào thị trấn, buộc phải lang thang nơi hoang dã. Dù đa số chỉ đang trả giá cho những lỗi lầm trong quá khứ, nhưng xét rằng các phiên tòa không phải lúc nào cũng "công bằng" ở mọi quốc gia, không ít kẻ lưu đày bị trục xuất oan uổng và ôm hận trong lòng.</t>
         </is>
       </c>
     </row>
@@ -24478,7 +24478,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Tên khoa học "Resinacrustidum lapis", Băng Tay Đá thuộc chi Resinacrustidum thường thấy ở vùng núi. Người ta cho rằng vật liệu cấu thành lớp vỏ đá của nó rất dồi dào ở những khu vực này. Tacet Discord này có kích thước khổng lồ, chiến đấu bằng cách đập hoặc Dodgem đá. Sức mạnh đáng nể của nó phải đánh đổi bằng tốc độ di chuyển chậm chạp.</t>
+          <t>Tên khoa học "Resinacrustidum lapis", Băng Tay Đá thuộc chi Resinacrustidum thường thấy ở vùng núi. Người ta cho rằng vật liệu cấu thành lớp vỏ đá của nó rất dồi dào ở những khu vực này. Tacet Discord này có kích thước khổng lồ, chiến đấu bằng cách đập hoặc ném đá. Sức mạnh đáng nể của nó phải đánh đổi bằng tốc độ di chuyển chậm chạp.</t>
         </is>
       </c>
     </row>
@@ -24803,7 +24803,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Tên khoa học ba phần "Ursus spelaeus sagispina", chủ yếu sinh sống tại Khu Rừng Huanglong. Sinh Vật Đột Biến này có thị lực kém và chủ yếu dựa vào thính giác để săn mồi.</t>
+          <t>Tên ba phần "Ursus spelaeus sagispina", chủ yếu sinh sống tại Rừng Huanglong. Sinh Vật Đột Biến này có thị lực kém và chủ yếu dựa vào thính giác để săn mồi.</t>
         </is>
       </c>
     </row>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Fractsidus Thruster không linh hoạt lắm. Đi vòng quanh nó sẽ khiến nó mất phương hướng. Nhưng nếu đi vòng quá nhiều, nó sẽ nổi giận và phản đòn bằng một cú đánh dữ dội. Nó có thể nhảy lên rồi đập mạnh xuống đất.</t>
+          <t>Động Cơ Phản Lực Fractsidus không linh hoạt lắm. Đi vòng quanh nó sẽ khiến nó mất phương hướng. Nhưng nếu đi vòng quá nhiều, nó sẽ nổi giận và phản đòn bằng một cú đánh dữ dội. Nó có thể nhảy lên rồi đập mạnh xuống đất.</t>
         </is>
       </c>
     </row>
@@ -25193,7 +25193,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Vua Không Vương Miện không lao vào giao chiến ngay từ đầu trận. Hắn thích thử thách sức mạnh và điểm yếu của đối thủ hơn. Bằng cách chịu đòn, hắn dần nắm bắt được lối tấn công của đối phương và bắt đầu Dodge. Một khi đã vào thế trận, hầu hết các đòn tấn công của hắn đều có thể bị phản đòn bằng Kỹ Năng Phản Công.</t>
+          <t>Vua Không Vương Miện không lao vào giao chiến ngay từ đầu trận. Hắn thích thử thách sức mạnh và điểm yếu của đối thủ hơn. Bằng cách chịu đòn, hắn dần nắm bắt được lối tấn công của đối phương và bắt đầu né tránh. Một khi đã vào thế trận, hầu hết các đòn tấn công của hắn đều có thể bị phản đòn bằng Kỹ Năng Phản Công.</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Trên đường đi, cậu hấp thụ một Echoes trực tiếp vào cơ thể. Khả năng kỳ lạ này thu hút sự chú ý của những người bạn mới. Chixia gợi ý cậu thu thập thêm Echoes trên đường đến Thành Jinzhou, nhưng lần thử thứ hai lại thất bại.
+          <t>Trên đường đi, cậu hấp thụ một Echo trực tiếp vào cơ thể. Khả năng kỳ lạ này thu hút sự chú ý của những người bạn mới. Chixia gợi ý cậu thu thập thêm Echo trên đường đến Thành Jinzhou, nhưng lần thử thứ hai lại thất bại.
 Không hiểu nguyên lý hoạt động, cậu tiếp tục hành trình đến Thành Jinzhou để tìm câu trả lời, mà không hay biết một cô gái bí ẩn đang theo dõi từng bước đi của cậu...</t>
         </is>
       </c>
@@ -25525,7 +25525,7 @@
       <c r="M384" t="inlineStr">
         <is>
           <t>Hành trình đưa cậu đến Tòa Thị chính, nơi Quan Phủ Jinzhou – Jinhsi – đã triệu tập. Nhưng Jinhsi không có mặt. Vệ sĩ của cô, Sanhua, trao cho cậu ba tín vật và hẹn gặp lại sau ba ngày.
-Yangyang giục cậu đến Huaxu Academy, nơi Baizhi làm việc, để tìm manh mối về những tín vật. Tại đó, tín vật đầu tiên hé lộ mối liên hệ trong quá khứ giữa cậu và Jinzhou.
+Yangyang giục cậu đến Học viện Huaxu, nơi Baizhi làm việc, để tìm manh mối về những tín vật. Tại đó, tín vật đầu tiên hé lộ mối liên hệ trong quá khứ giữa cậu và Jinzhou.
 Hành động của cậu dường như thu hút quá nhiều ánh nhìn. Ai là thợ săn, ai là con mồi?</t>
         </is>
       </c>
@@ -25595,7 +25595,7 @@
         <is>
           <t>Mảnh ghép thứ hai dẫn cậu và Yangyang đến một nơi ngoài thành phố.
 Trên đường ra ngoài, các cậu gặp Jianxin, một đạo sĩ trẻ đang tìm người mất tích. Nhờ quyền hạn của cậu, các cậu đưa cô ấy vượt qua tường thành. Cả ba đến Trại Hậu Cần Midnight Rangers, nơi bóng chiến tranh đang phủ xuống chân trời. Những manh mối từ viên quản lý tiết lộ rằng mảnh ghép thứ hai này có liên quan đến cuộc chiến sắp tới.
-Sau khi giải quyết xong, cậu bị cuốn vào ảo giác. Khi tỉnh lại, lời của Yangyang giúp cậu nhận ra mảnh ghép cuối cùng dẫn đến đâu: làng Qichi ở Central Plains.</t>
+Sau khi giải quyết xong, cậu bị cuốn vào ảo giác. Khi tỉnh lại, lời của Yangyang giúp cậu nhận ra mảnh ghép cuối cùng dẫn đến đâu: Qichi Village in the Central Plains.</t>
         </is>
       </c>
     </row>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Khi cậu và Yangyang đến làng Qichi, các người sững sờ khi thấy nơi đây đã biến thành một Tacet Field. Cuộc điều tra của các người bị cắt ngang bởi Scar, một Giám Sát Viên của Fractsidus. Hắn tiết lộ bi kịch đã xảy ra với làng Qichi và mời cậu gia nhập hắn. Cậu từ chối, và cuộc đối đầu leo thang thành trận chiến.
+          <t>Khi cậu và Yangyang đến làng Qichi, các người sững sờ khi thấy nơi đây đã biến thành một Tổ Tacet. Cuộc điều tra của các người bị cắt ngang bởi Scar, một Giám Sát Viên của Fractsidus. Hắn tiết lộ bi kịch đã xảy ra với làng Qichi và mời cậu gia nhập hắn. Cậu từ chối, và cuộc đối đầu leo thang thành trận chiến.
 Trong hỗn loạn, một cô gái bí ẩn xuất hiện che chắn cho Scar rút lui. Sau khi thu thập đủ thông tin về cả ba tín vật, cậu trở về thành phố Jinzhou.</t>
         </is>
       </c>
@@ -25796,9 +25796,9 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Cậu tìm thấy Aalto và Encore, hai Nhà Tư Vấn của Bờ Đen. Aalto đồng ý kể cho cậu về nguồn gốc của mình, nhưng chỉ với điều kiện cậu cùng họ điều tra Ruins Tòa Án Savantae.
-Tại đó, cậu phát hiện Tòa Án Savantae từng cố sử dụng một cơn Retroact Rain nhân tạo để truy ngược thời gian tìm kiếm điều gì đó, nhưng thí nghiệm thất bại, tạo ra một con quái vật. Sau khi đánh bại nó, Aalto tiết lộ rằng hành trình của cậu từng đưa cậu đến Bờ Đen trước đây.
-Ngay lúc đó, một cơn Retroact Rain thật sự bắt đầu rơi, và một đợt Tacet Discord ập đến tấn công Thành phố Jinzhou.</t>
+          <t>Cậu tìm thấy Aalto và Encore, hai Nhà Tư Vấn của Bờ Đen. Aalto đồng ý kể cho cậu về nguồn gốc của mình, nhưng chỉ với điều kiện cậu cùng họ điều tra Tàn Tích Tòa Án Savantae.
+Tại đó, cậu phát hiện Tòa Án Savantae từng cố sử dụng một cơn Mưa Retroact nhân tạo để truy ngược thời gian tìm kiếm điều gì đó, nhưng thí nghiệm thất bại, tạo ra một con quái vật. Sau khi đánh bại nó, Aalto tiết lộ rằng hành trình của cậu từng đưa cậu đến Bờ Đen trước đây.
+Ngay lúc đó, một cơn Mưa Retroact thật sự bắt đầu rơi, và một đợt Tacet Discord ập đến tấn công Thành phố Jinzhou.</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
         <is>
           <t>Jinhsi biến mất khi tự mình đi kiểm tra an nguy của Sentinel. Cậu và Changli lên đường đến Núi Firmament để tìm nàng.
 Trên núi, thời gian như xoáy vào hỗn loạn. Jinhsi từ chối đề nghị hy sinh của Jué, quyết định chiến đấu với Sentinel như số phận đã định. Cậu chứng kiến trận chiến của nàng, và với sự đồng ý của cậu, Jué chuyển giao Quyền Lệnh Thời Gian cho Jinhsi, trả lại tương lai của Jinzhou cho người dân nơi đây.
-Khi mọi chuyện kết thúc, Jué gợi ý cậu đến Black Shores để khám phá quá khứ của cậu và Abby.</t>
+Khi mọi chuyện kết thúc, Jué gợi ý cậu đến Bờ Biển Đen để khám phá quá khứ của cậu và Abby.</t>
         </is>
       </c>
     </row>
@@ -26134,8 +26134,8 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Yangyang, Chixia và Baizhi mời bạn tham gia Moon-Chasing Festival cùng họ. Tại Cây Wish, bạn gặp Xiangli Yao và biết rằng anh chính là người bí ẩn ban điều ước. Bạn đồng ý giúp anh điều tra bốn điều ước chứa dữ liệu bất thường.
-Cùng nhau, các bạn khám phá Quả Cầu Sonoro bất thường, vén màn quá khứ của Xiangli Yao và giải quyết vấn đề của những người gửi gắm điều ước. Kết thúc lễ hội, bạn và bạn bè chụp một bức ảnh kỷ niệm dưới ánh trăng.</t>
+          <t>Yangyang, Chixia và Baizhi mời bạn tham gia Lễ Hội Đuổi Trăng cùng họ. Tại Cây Ước Nguyện, bạn gặp Xiangli Yao và biết rằng anh chính là người bí ẩn ban điều ước. Bạn đồng ý giúp anh điều tra bốn điều ước chứa dữ liệu bất thường.
+Cùng nhau, các bạn khám phá Sonoro Sphere bất thường, vén màn quá khứ của Xiangli Yao và giải quyết vấn đề của những người gửi gắm điều ước. Kết thúc lễ hội, bạn và bạn bè chụp một bức ảnh kỷ niệm dưới ánh trăng.</t>
         </is>
       </c>
     </row>
@@ -26203,7 +26203,7 @@
       <c r="M394" t="inlineStr">
         <is>
           <t>Theo sự chỉ dẫn từ chính bản thân quá khứ và hệ thống Tethys, cậu lên đường đến Rinascita để tìm Imperator và tìm giải pháp cho tình trạng tần số của Abby ngày càng suy yếu.
-Cetus the Tidebreaker tấn công trên biển, nhưng Brant, thuyền trưởng của Fool's Troupe, đã giúp cậu vượt qua màn sương mù. Hai người hẹn gặp lại nhau tại lễ khai mạc Carnevale.
+Cetus Kẻ Phá Thủy Triều tấn công trên biển, nhưng Brant, thuyền trưởng của Fool's Troupe, đã giúp cậu vượt qua màn sương mù. Hai người hẹn gặp lại nhau tại lễ khai mạc Carnevale.
 Khi đến Ragunna, cậu chứng kiến những cuộc "hành hương" kỳ lạ, và một nhà viết kịch bước ra giải thích nguồn gốc của chúng.</t>
         </is>
       </c>
@@ -26269,7 +26269,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Dưới sự dẫn dắt của Acolyte Phoebe, cậu bước vào thành phố Echoes này và dần hiểu được tầm quan trọng của Echoes đối với Rinascita. Trong lúc xử lý gia tộc Montelli – những người đã gửi lời mời đến Black Shores – cậu đồng điệu với một Vitreum Dancer mất kiểm soát và nhận được lời cầu cứu từ Sentinel. Khi điều tra nguyên nhân vụ việc, cậu thoáng thấy những dòng chảy ngầm bên dưới Ragunna: những giao dịch bí mật giữa Order, giới quý tộc và Fractsidus. Phrolova, một Fractsidus Overseer mà cậu từng gặp thoáng qua, cũng đang dõi theo từ bóng tối.</t>
+          <t>Dưới sự dẫn dắt của Tín Đồ Phoebe, cậu bước vào thành phố Echoes này và dần hiểu được tầm quan trọng của Echoes đối với Rinascita. Trong lúc xử lý gia tộc Montelli – những người đã gửi lời mời đến Black Shores – cậu đồng điệu với một Vitreum Dancer mất kiểm soát và nhận được lời cầu cứu từ Sentinel. Khi điều tra nguyên nhân vụ việc, cậu thoáng thấy những dòng chảy ngầm bên dưới Ragunna: những giao dịch bí mật giữa Order, giới quý tộc và Fractsidus. Phrolova, một Fractsidus Overseer mà cậu từng gặp thoáng qua, cũng đang dõi theo từ bóng tối.</t>
         </is>
       </c>
     </row>
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Trên cây cầu dẫn đến hòn đảo, cậu bị Dragon Dirge tấn công, và Roccia của Fool's Troupe đã đến trợ giúp. Tại Penitent's End, cậu biết được sự thật đằng sau những "cuộc hành hương" và hội ngộ với Carlotta. Cậu quyết định hợp tác với Fool's Troupe để giành lấy vòng nguyệt quế tại Carnevale. Tuy nhiên, Phrolova đã ra tay phá hoại lễ hội.
+          <t>Trên cây cầu dẫn đến hòn đảo, cậu bị Rồng Dirge tấn công, và Roccia của Fool's Troupe đã đến trợ giúp. Tại Penitent's End, cậu biết được sự thật đằng sau những "cuộc hành hương" và hội ngộ với Carlotta. Cậu quyết định hợp tác với Fool's Troupe để giành lấy vòng nguyệt quế tại Carnevale. Tuy nhiên, Phrolova đã ra tay phá hoại lễ hội.
 Sau khi đánh bại cô ta, cuối cùng cậu cũng được gặp Sentinel, người tiết lộ rằng "Những Kẻ Lạc Lối"—họ mong cậu giúp đỡ—đang ở giữa đám đông tại Carnevale.</t>
         </is>
       </c>
@@ -26803,7 +26803,7 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>Ragunna bị Tối Triều tấn công, sinh vật của nó xuất hiện khắp thành phố. Avidius cùng cậu truy đuổi, nhưng trong quá trình đó, hắn dần phát hiện ra sự thật về bản thân mình. Vào giây phút cuối đời, hắn hấp thụ Tối Triều và chấm dứt cuộc khủng hoảng ở Ragunna.
-Chính lúc đó, cậu mới nhận ra mình đã bị Tối Triều bí mật tha hóa từ lâu và giờ đây đã trở thành Harbinger Leviathan. Để chấm dứt cuộc khủng hoảng một lần và mãi mãi, cậu lại lên đường đến Septimont cùng Kẻ Sát Discord bí ẩn Galbrena.</t>
+Chính lúc đó, cậu mới nhận ra mình đã bị Tối Triều bí mật tha hóa từ lâu và giờ đây đã trở thành Sứ Giả Leviathan. Để chấm dứt cuộc khủng hoảng một lần và mãi mãi, cậu lại lên đường đến Septimont cùng Kẻ Sát Discord bí ẩn Galbrena.</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26869,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Một đợt Triều High bất thường ập vào Septimont. Để ngăn chặn Hắc Triều, người dân Ragunna kéo đến hỗ trợ thành phố, còn Bờ Đen cử tất cả Bloom Bearer còn khả năng chiến đấu. Galbrena lao thẳng vào Hắc Triều. Ngươi và đồng đội cũng nhanh chóng theo chân, lao xuống cùng chiếc đèn lồng do Qiuyuan mang đến.
+          <t>Một đợt Triều Cao bất thường ập vào Septimont. Để ngăn chặn Hắc Triều, người dân Ragunna kéo đến hỗ trợ thành phố, còn Bờ Đen cử tất cả Bloom Bearer còn khả năng chiến đấu. Galbrena lao thẳng vào Hắc Triều. Ngươi và đồng đội cũng nhanh chóng theo chân, lao xuống cùng chiếc đèn lồng do Qiuyuan mang đến.
 Sau bao gian khổ, cuối cùng ngươi cũng nhìn thấy ánh sáng hy vọng. Ngươi cùng người dân Rinascita đánh bại Threnodian được hồi sinh bởi Viên Ngọc. Rinascita cuối cùng cũng có được bình yên xứng đáng.</t>
         </is>
       </c>
@@ -27001,7 +27001,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Khi Bóng Tối Tràn Đến, theo yêu cầu cá nhân từ một người ở Mingting, Qiuyuan đã đến Ragunna để hỗ trợ ngươi. Sau khi giải cứu một Acolyte ở Ragunna, anh ấy đến Xưởng Dệt Sâu, thuyết phục Fenrico giao nộp Di Vật Đầu Tiên – công cụ then chốt để ngăn chặn Bóng Tối. Rồi anh ấy kịp thời có mặt trong trận chiến cuối để trao Di Vật cho ngươi.
+          <t>Khi Bóng Tối Tràn Đến, theo yêu cầu cá nhân từ một người ở Mingting, Qiuyuan đã đến Ragunna để hỗ trợ ngươi. Sau khi giải cứu một Tín Đồ ở Ragunna, anh ấy đến Xưởng Dệt Sâu, thuyết phục Fenrico giao nộp Di Vật Đầu Tiên – công cụ then chốt để ngăn chặn Bóng Tối. Rồi anh ấy kịp thời có mặt trong trận chiến cuối để trao Di Vật cho ngươi.
 Sau chiến tranh, Ciaccona kể lại những chiến công của Qiuyuan ở Rinascita. Sau đó, ngươi tìm thấy Qiuyuan ở bến tàu khi anh ấy chuẩn bị rời đi và bày tỏ lòng biết ơn.</t>
         </is>
       </c>
@@ -27132,7 +27132,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Ngươi đến Black Shores thăm Chisa, nhưng lại phát hiện ra trong Cooldown phục, cô đã bí mật một mình đến Honami City. Với gánh nặng của sự thật rằng hơn hai thập kỷ đã trôi qua ở thế giới bên ngoài, cô cảm thấy bất an về tương lai. Cùng nhau, hai người dạo bước qua Sakura Quarter để xoa dịu tâm trạng cô. Dưới những cánh hoa rơi, cô thổ lộ tâm tư với ngươi và trao lại thẻ học sinh cũ của ngươi cùng một món quà chuẩn bị kỹ lưỡng. Ngạc nhiên thay, ngươi phát hiện mình từng là học sinh của Startorch Academy. Sau đó, Chisa đề nghị mời bạn bè từ Black Shores đến Shashou Cafe để chính thức "khai trương" quán…</t>
+          <t>Ngươi đến Black Shores thăm Chisa, nhưng lại phát hiện ra trong thời gian hồi phục, cô đã bí mật một mình đến Honami City. Với gánh nặng của sự thật rằng hơn hai thập kỷ đã trôi qua ở thế giới bên ngoài, cô cảm thấy bất an về tương lai. Cùng nhau, hai người dạo bước qua Sakura Quarter để xoa dịu tâm trạng cô. Dưới những cánh hoa rơi, cô thổ lộ tâm tư với ngươi và trao lại thẻ học sinh cũ của ngươi cùng một món quà chuẩn bị kỹ lưỡng. Ngạc nhiên thay, ngươi phát hiện mình từng là học sinh của Startorch Academy. Sau đó, Chisa đề nghị mời bạn bè từ Black Shores đến Shashou Cafe để chính thức "khai trương" quán…</t>
         </is>
       </c>
     </row>
@@ -27199,7 +27199,7 @@
       <c r="M409" t="inlineStr">
         <is>
           <t>Lối vào Lahai-Roi cuối cùng cũng mở ra. Sau khi chia tay Namipon và Shorekeeper, Chisa và cậu lần lượt bước vào đường hầm. Trên đường đi, cả hai bị cuốn vào một thế giới bí ẩn nơi có một Threnodian trú ngụ. Ngay khi tần số của cậu sắp bị nuốt chửng, một cô gái tóc hồng xuất hiện, giải cứu rồi đưa các cậu trở lại thực tại.
-Đến Lahai-Roi, cậu bất ngờ gặp lại một nữ sinh tên Lynae. Cô ấy đến trên chiếc mô tô của mình, giúp cậu thoát khỏi cuộc tấn công của Voidworm, và đưa cậu an toàn đến đích – Startorch Academy.</t>
+Đến Lahai-Roi, cậu bất ngờ gặp lại một nữ sinh tên Lynae. Cô ấy đến trên chiếc mô tô của mình, giúp cậu thoát khỏi cuộc tấn công của Voidworm, và đưa cậu an toàn đến đích – Học viện Startorch.</t>
         </is>
       </c>
     </row>
@@ -27264,7 +27264,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Sau khi hoàn tất thủ tục nhập học, cậu chính thức trở thành học viên của Startorch Academy. Tại Viện Nghiên Cứu, cậu gặp Giáo sư Mornye và biết rằng Spacetrek Collective đang chuẩn bị cho dự án trọng đại - New Solar Ceremony. Nhưng chưa kịp lâu, cậu đã bị cuốn vào sự cố do Hyvatia đột ngột trục trặc. Lynae - người có mặt tại hiện trường - lập tức bị tình nghi, và hai người cùng nhau bắt đầu điều tra sự thật đằng sau hỗn loạn. Cuộc điều tra hé lộ thân phận thật của Lynae cùng âm mưu của Fractsidus. Cuối cùng, cậu và Lynae dụ được và đánh bại Voidworm đang đe dọa Học viện, giải quyết nguy cơ trước mắt. Thế nhưng, những kẻ chủ mưu vẫn lẩn khuất, và kế hoạch của chúng còn lâu mới kết thúc.</t>
+          <t>Sau khi hoàn tất thủ tục nhập học, cậu chính thức trở thành học viên của Học viện Startorch. Tại Viện Nghiên cứu, cậu gặp Giáo sư Mornye và biết rằng Spacetrek Collective đang chuẩn bị cho dự án trọng đại - Lễ Hội Mặt Trời Mới. Nhưng chưa kịp lâu, cậu đã bị cuốn vào sự cố do Hyvatia đột ngột trục trặc. Lynae - người có mặt tại hiện trường - lập tức bị tình nghi, và hai người cùng nhau bắt đầu điều tra sự thật đằng sau hỗn loạn. Cuộc điều tra hé lộ thân phận thật của Lynae cùng âm mưu của Fractsidus. Cuối cùng, cậu và Lynae dụ được và đánh bại Voidworm đang đe dọa Học viện, giải quyết nguy cơ trước mắt. Thế nhưng, những kẻ chủ mưu vẫn lẩn khuất, và kế hoạch của chúng còn lâu mới kết thúc.</t>
         </is>
       </c>
     </row>
@@ -27329,7 +27329,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Khi New Solar Ceremony sắp đến, cậu nhận được lời cầu cứu, người gửi gọi cậu là Arbiter. Nghi ngờ có liên quan đến New Solar Ceremony, Mornye cùng cậu đến Bjartr Woods để tìm hiểu sự thật. Tại đó, cậu phát hiện Fractsidus đã lừa dối Roya Tribe kích hoạt sự sụp đổ của Reactor Drive. Để đảm bảo vụ phóng mặt trời nhân tạo "Helios" thành công, Mornye tự mình bước vào Drive. Khi bụi mù tan đi, một bình minh mới cuối cùng cũng ló dạng trên Lahai-Roi.</t>
+          <t>Khi Lễ Hội Mặt Trời Mới sắp đến, cậu nhận được lời cầu cứu, người gửi gọi cậu là Arbiter. Nghi ngờ có liên quan đến Lễ Hội Mặt Trời Mới, Mornye cùng cậu đến Bjartr Woods để tìm hiểu sự thật. Tại đó, cậu phát hiện Fractsidus đã lừa dối Bộ Lạc Roya kích hoạt sự sụp đổ của Reactor Drive. Để đảm bảo vụ phóng mặt trời nhân tạo "Helios" thành công, Mornye tự mình bước vào Drive. Khi bụi mù tan đi, một bình minh mới cuối cùng cũng ló dạng trên Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -27394,7 +27394,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Sau khi hành trình đến Roya Frostlands kết thúc, cậu đến phòng bệnh để thảo luận kế hoạch Exostrider với Luuk Herssen. Trong xưởng bí mật của anh, Luuk giải thích tình trạng hiện tại của Fractsidus và lý do anh đến Lahai-Roi. Một thành viên Fractsidus đã bắt cóc học sinh Royan từng đồng hành cùng cậu, đưa cô đến trạm không gian bỏ hoang. Cả hai cùng hợp sức giải quyết khủng hoảng. Tuy nhiên, trong nhiệm vụ, cậu phát hiện một đặc vụ Fractsidus khác vẫn đang ẩn náu trong Học Viện, chờ đợi New Solar Ceremony bắt đầu. Được an ủi bởi lời của Luuk Herssen, cậu nhận viên kẹo anh đưa, và với quyết tâm mới, cậu lấy lại được sự bình tâm và lòng kiên định.</t>
+          <t>Sau khi hành trình đến Roya Frostlands kết thúc, cậu đến phòng bệnh để thảo luận kế hoạch Exostrider với Luuk Herssen. Trong xưởng bí mật của anh, Luuk giải thích tình trạng hiện tại của Fractsidus và lý do anh đến Lahai-Roi. Một thành viên Fractsidus đã bắt cóc học sinh Royan từng đồng hành cùng cậu, đưa cô đến trạm không gian bỏ hoang. Cả hai cùng hợp sức giải quyết khủng hoảng. Tuy nhiên, trong nhiệm vụ, cậu phát hiện một đặc vụ Fractsidus khác vẫn đang ẩn náu trong Học Viện, chờ đợi Lễ Hội Mặt Trời Mới bắt đầu. Được an ủi bởi lời của Luuk Herssen, cậu nhận viên kẹo anh đưa, và với quyết tâm mới, cậu lấy lại được sự bình tâm và lòng kiên định.</t>
         </is>
       </c>
     </row>
@@ -27460,7 +27460,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Với Lễ Kỷ Niệm Mặt Trời New sắp đến gần, trò chơi mà Kiến Trúc Sư Cấp Cao của Fractsidus nhắc đến như một bóng đen ẩn hiện trên Học Viện. Cùng với Sigrika, ngươi lên đường điều tra tần số bí ẩn ở Mặt Tối và giải mã những bí ẩn xung quanh nó.
+          <t>Với Lễ Kỷ Niệm Mặt Trời Mới sắp đến gần, trò chơi mà Kiến Trúc Sư Cấp Cao của Fractsidus nhắc đến như một bóng đen ẩn hiện trên Học Viện. Cùng với Sigrika, ngươi lên đường điều tra tần số bí ẩn ở Mặt Tối và giải mã những bí ẩn xung quanh nó.
 Hợp sức lại, các ngươi đánh bại xoáy nước còn sót lại ở Mặt Tối, khôi phục sự yên tĩnh tạm thời. Nhưng ngươi không thể xua đi cảm giác rằng vẫn còn nhiều bóng tối ẩn nấp, chờ đợi dưới vẻ bình yên của buổi tối để ngươi phải đối mặt.</t>
         </is>
       </c>
@@ -27526,7 +27526,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Trước khi khởi hành bảo vệ Dimmr Plains, Hiyuki một mình đến Honami. Trong lúc giúp Bờ Đen giải quyết những vấn đề còn dang dở của Left Behind, cô cũng tìm kiếm dấu vết của Miko Bông Anh Đào trước đây. Tại đó, cô bất ngờ chạm trán với Grand Architect của Fractsidus. Dù đối mặt với những lời kích động của hắn, Hiyuki vẫn không rút kiếm…</t>
+          <t>Trước khi khởi hành bảo vệ Đồng Bằng Dimmr, Hiyuki một mình đến Honami. Trong lúc giúp Bờ Đen giải quyết những vấn đề còn dang dở của Left Behind, cô cũng tìm kiếm dấu vết của Miko Bông Anh Đào trước đây. Tại đó, cô bất ngờ chạm trán với Kiến Trúc Sư Vĩ Đại của Fractsidus. Dù đối mặt với những lời kích động của hắn, Hiyuki vẫn không rút kiếm…</t>
         </is>
       </c>
     </row>
@@ -27721,7 +27721,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Denia, người bị bắt giữ sau trận chiến cuối, giờ đã tỉnh lại. Tập thể Spacetrek hy vọng hợp tác với cô ấy và giao cho cậu nhiệm vụ đàm phán. Sau khi trò chuyện, cậu đạt được thỏa thuận: cô ấy đồng ý giúp Tập thể và kể cho cậu nghe những gì mình biết về Grand Architect, đổi lại, cậu sẽ cùng cô ấy đón sinh nhật tại Học viện. Đêm đó, Denia cuối cùng cũng tiết lộ sự thật về con người thật của mình. Không có câu trả lời dễ dàng cho tình cảnh của cô ấy, nhưng cậu đã nói từ trái tim, và điều đó đã tiếp thêm dũng khí cho cô.</t>
+          <t>Denia, người bị bắt giữ sau trận chiến cuối, giờ đã tỉnh lại. Tập thể Spacetrek hy vọng hợp tác với cô ấy và giao cho cậu nhiệm vụ đàm phán. Sau khi trò chuyện, cậu đạt được thỏa thuận: cô ấy đồng ý giúp Tập thể và kể cho cậu nghe những gì mình biết về Kiến Trúc Sư Vĩ Đại, đổi lại, cậu sẽ cùng cô ấy đón sinh nhật tại Học viện. Đêm đó, Denia cuối cùng cũng tiết lộ sự thật về con người thật của mình. Không có câu trả lời dễ dàng cho tình cảnh của cô ấy, nhưng cậu đã nói từ trái tim, và điều đó đã tiếp thêm dũng khí cho cô.</t>
         </is>
       </c>
     </row>
@@ -28186,7 +28186,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Uncle Li ở Yumyum Haven là một người đam mê thử nghiệm các công thức nấu ăn để chiều lòng thực khách. Vì thế, ông luôn tìm kiếm những nguyên liệu hiếm. Với niềm tin vào tri thức từ thực tiễn, ông đã biên soạn Cẩm Nang Nguyên Liệu và mong muốn có người kế thừa công trình của mình.</t>
+          <t>Bác Lý ở Thiên Đường Ẩm Thực là một người đam mê thử nghiệm các công thức nấu ăn để chiều lòng thực khách. Vì thế, ông luôn tìm kiếm những nguyên liệu hiếm. Với niềm tin vào tri thức từ thực tiễn, ông đã biên soạn Cẩm Nang Nguyên Liệu và mong muốn có người kế thừa công trình của mình.</t>
         </is>
       </c>
     </row>
@@ -28318,7 +28318,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Truyền thuyết kể rằng Dodgem đồ vật vào hốc cây sẽ khiến chúng được hồi phục, nên mới có đống đồ cũ chất đống ở đó. Mỗi vết nứt, mỗi vết sứt trên chúng đều lặng lẽ kể lại câu chuyện của quá khứ.</t>
+          <t>Truyền thuyết kể rằng ném đồ vật vào hốc cây sẽ khiến chúng được hồi phục, nên mới có đống đồ cũ chất đống ở đó. Mỗi vết nứt, mỗi vết sứt trên chúng đều lặng lẽ kể lại câu chuyện của quá khứ.</t>
         </is>
       </c>
     </row>
@@ -28582,7 +28582,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Một đoàn biểu diễn độc đáo vừa đặt chân đến Thung Lũng Taoyuan. Học viện hy vọng sẽ giới thiệu một số Echoes đáng yêu và duyên dáng trong các tiết mục của Hội Chợ Trăng Sáng, nhằm làm nổi bật tiềm năng của Echoes trước khán giả. Để đảm bảo Echoes biểu diễn ổn định, họ cần người hỗ trợ bắt giữ những Echoes cụ thể và thu thập dữ liệu liên quan.</t>
+          <t>Một đoàn biểu diễn độc đáo vừa đặt chân đến Thung Lũng Taoyuan. Học viện hy vọng sẽ giới thiệu một số Echo đáng yêu và duyên dáng trong các tiết mục của Hội Chợ Trăng Sáng, nhằm làm nổi bật tiềm năng của Echo trước khán giả. Để đảm bảo Echo biểu diễn ổn định, họ cần người hỗ trợ bắt giữ những Echo cụ thể và thu thập dữ liệu liên quan.</t>
         </is>
       </c>
     </row>
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Soldiers đóng quân tại biên giới đã gửi gắm nguyện vọng của mình đến Moontree Lodge—những bức ảnh, món ăn quê hương, và nhu yếu phẩm thiết yếu. Nếu có thời điểm nào để biến những nguyện vọng ấy thành hiện thực, thì đó chính là dịp Hội Trăng Rằm.</t>
+          <t>Những người lính đóng quân tại biên giới đã gửi gắm nguyện vọng của mình đến Moontree Lodge—những bức ảnh, món ăn quê hương, và nhu yếu phẩm thiết yếu. Nếu có thời điểm nào để biến những nguyện vọng ấy thành hiện thực, thì đó chính là dịp Hội Trăng Rằm.</t>
         </is>
       </c>
     </row>
@@ -28909,7 +28909,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Moonlit Fair tại Taoyuan Vale là dịp để du khách tìm hiểu phong tục tập quán địa phương ở Jinzhou. Để giúp du khách lần đầu trải nghiệm trọn vẹn Moon-Chasing Festival, Taoyuan Vale đang tìm kiếm những hướng dẫn viên du lịch để làm phong phú thêm chuyến thăm của họ.</t>
+          <t>Hội Chợ Ánh Trăng tại Thung Lũng Đào Nguyên là dịp để du khách tìm hiểu phong tục tập quán địa phương ở Jinzhou. Để giúp du khách lần đầu trải nghiệm trọn vẹn Lễ Hội Đuổi Trăng, Thung Lũng Đào Nguyên đang tìm kiếm những hướng dẫn viên du lịch để làm phong phú thêm chuyến thăm của họ.</t>
         </is>
       </c>
     </row>
@@ -29108,7 +29108,7 @@
       <c r="M438" t="inlineStr">
         <is>
           <t>"\"Vầng Trăng Phán Xử\" nơi bạn được trải nghiệm bói toán truyền thống của Huanglong. Ánh trăng soi bóng nước sẽ tiên đoán điều kỳ diệu gì cho bạn? Nếu không thích, vẫn còn nhiều phương pháp bói toán khác như xem bói.
-&lt;color=#a5a19d&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để trải nghiệm mini-game và nhận buff hàng ngày.&lt;/color&gt;"</t>
+&lt;color=#a5a19d&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm mini-game và nhận buff hàng ngày.&lt;/color&gt;"</t>
         </is>
       </c>
     </row>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Cây Sào Hoa Mai là nền tảng huấn luyện của Liondance Troupe. Những vũ công Lân tương lai phải đi trên những chiếc sào này với sự thoải mái như trên mặt đất.
+          <t>Cây Sào Hoa Mai là nền tảng huấn luyện của Đoàn Múa Lân. Những vũ công Lân tương lai phải đi trên những chiếc sào này với sự thoải mái như trên mặt đất.
 &lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng.&lt;/color&gt;</t>
         </is>
       </c>
@@ -29241,8 +29241,8 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Yumyum Haven mang đến vô vàn đặc sản địa phương hấp dẫn, trong đó nổi tiếng nhất là món Bánh Béo Ngậy.
-&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
+          <t>Thiên Đường Ẩm Thực mang đến vô vàn đặc sản địa phương hấp dẫn, trong đó nổi tiếng nhất là món Bánh Béo Ngậy.
+&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29309,7 +29309,7 @@
       <c r="M441" t="inlineStr">
         <is>
           <t>Pháo hoa từ lâu đã là truyền thống yêu thích ở Huanglong, thắp sáng bầu trời rực rỡ sắc màu trong mỗi dịp lễ hội.
-&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
+&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để mua các vật phẩm sự kiện độc quyền.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29375,7 +29375,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Thử thách "Echo: Gulpuff" cực hot từ Jinzhou nay đã có mặt tại Moonlit Fair!
+          <t>Thử thách "Tiếng Vọng: Gulpuff" cực hot từ Jinzhou nay đã có mặt tại Hội Chợ Ánh Trăng!
 &lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Điểm Nổi Tiếng đáng kể. Hãy ghé thăm gian hàng để trải nghiệm các mini-game và nhận thưởng.&lt;/color&gt;</t>
         </is>
       </c>
@@ -29510,7 +29510,7 @@
       <c r="M444" t="inlineStr">
         <is>
           <t>Gian hàng giải trí lấy cảm hứng từ Sentinel Hsin. Có tin đồn rằng gian hàng này tặng phần thưởng bất ngờ.
-&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng để tăng đáng kể Độ Nổi Tiếng. Visit gian hàng để trải nghiệm mini-game và nhận phần thưởng hàng ngày.&lt;/color&gt;</t>
+&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng để tăng đáng kể Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm mini-game và nhận phần thưởng hàng ngày.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29644,7 +29644,7 @@
       <c r="M446" t="inlineStr">
         <is>
           <t>Câu đố là sự kết hợp hoàn hảo giữa giải trí và thử thách trí tuệ. Giải được chúng mang lại niềm hứng khởi vượt xa những phần thưởng hữu hình.
-&lt;color=#a5a19d&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để trải nghiệm mini-game và nhận thưởng hàng ngày.&lt;/color&gt;</t>
+&lt;color=#a5a19d&gt;Xây dựng hoặc nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm mini-game và nhận thưởng hàng ngày.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29711,7 +29711,7 @@
       <c r="M447" t="inlineStr">
         <is>
           <t>Dù nguồn gốc của Moon Shooter đã bị thời gian vùi lấp, nhưng lối chơi đơn giản cùng những chuỗi điểm số gây nghiện của nó đã nhận được vô số lời khen ngợi. 
-&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Visit gian hàng để trải nghiệm các mini-game và nhận phần thưởng.&lt;/color&gt;</t>
+&lt;color=#a5a19d&gt;Xây dựng hoặc Nâng cấp gian hàng này để tăng Độ Nổi Tiếng. Ghé thăm gian hàng để trải nghiệm các mini-game và nhận phần thưởng.&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -29845,7 +29845,7 @@
       <c r="M449" t="inlineStr">
         <is>
           <t>Ban đầu, Jiyan không hề giỏi cầm giáo.
-Like các Midnight Ranger khác, cậu ấy chỉ được huấn luyện dùng kiếm. Nhưng trong trận chiến định mệnh đó, khi đứng lên dẫn dắt đồng đội thoát khỏi tình thế nguy khốn, gió đã hóa thành cây giáo dài mà cậu ấy sử dụng đến tận bây giờ.</t>
+Giống như các Midnight Ranger khác, cậu ấy chỉ được huấn luyện dùng kiếm. Nhưng trong trận chiến định mệnh đó, khi đứng lên dẫn dắt đồng đội thoát khỏi tình thế nguy khốn, gió đã hóa thành cây giáo dài mà cậu ấy sử dụng đến tận bây giờ.</t>
         </is>
       </c>
     </row>
@@ -29913,9 +29913,9 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Lucky Greetings Collection do Lingyang biên soạn đã trở thành cuốn sách gối đầu giường của Liondance Troupe.
+          <t>Bộ Sưu Tập Lời Chúc May Mắn do Lingyang biên soạn đã trở thành cuốn sách gối đầu giường của Đoàn Múa Lân.
 "Các bà mẹ sẽ không còn lo con mình lúng túng khi chúc Tết nữa!"
-"'Trăng sáng trên cao, trong trẻo lung linh, đêm nay ta quây quần bên ánh trăng.' Thật là một lời chúc đẹp! Học thuộc Chương 13, và cậu sẽ chẳng còn sợ gì khi đến thăm các bậc trưởng bối trong Moon-Chasing Festival!"
+"'Trăng sáng trên cao, trong trẻo lung linh, đêm nay ta quây quần bên ánh trăng.' Thật là một lời chúc đẹp! Học thuộc Chương 13, và cậu sẽ chẳng còn sợ gì khi đến thăm các bậc trưởng bối trong Lễ Hội Đuổi Trăng!"
 Cuối sách, ngày càng nhiều lời giới thiệu chân thành từ các thành viên trong đoàn được bổ sung.</t>
         </is>
       </c>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Mỗi món ăn đều có Dodget độc đáo riêng. Thật khó để chọn ra một món, nhưng nếu phải chọn, đó sẽ là bữa ăn tôi nhận được khi còn nhỏ, trong cơn đói khát—một nghĩa cử tử tế đã để lại dấu ấn không thể phai mờ. Hương vị ấy vẫn còn đọng mãi trong tôi đến tận bây giờ.</t>
+          <t>Mỗi món ăn đều có nét độc đáo riêng. Thật khó để chọn ra một món, nhưng nếu phải chọn, đó sẽ là bữa ăn tôi nhận được khi còn nhỏ, trong cơn đói khát—một nghĩa cử tử tế đã để lại dấu ấn không thể phai mờ. Hương vị ấy vẫn còn đọng mãi trong tôi đến tận bây giờ.</t>
         </is>
       </c>
     </row>
@@ -31888,9 +31888,9 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Resonators 5-Star
-◇ Tỷ lệ rơi cơ bản của Resonators 5-Star là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
-◇ Mỗi khi nhận được Resonators 5-Star, có 50,00000% cơ hội đó sẽ là Resonators 5-Star Nổi Bật của banner sự kiện này, và 50,00000% cơ hội nhận được một Resonators 5-Star không Nổi Bật ngẫu nhiên. Tất cả Resonators 5-Star không Nổi Bật đều có tỷ lệ rơi như nhau.</t>
+          <t>Resonator 5 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator 5 Sao là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
+◇ Mỗi khi nhận được Resonator 5 Sao, có 50,00000% cơ hội đó sẽ là Resonator 5 Sao Nổi Bật của banner sự kiện này, và 50,00000% cơ hội nhận được một Resonator 5 Sao không Nổi Bật ngẫu nhiên. Tất cả Resonator 5 Sao không Nổi Bật đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -31957,9 +31957,9 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Vũ Khí 5-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 5-Star là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
-◇ Mỗi khi nhận được Vũ Khí 5-Star, chắc chắn đó sẽ là Vũ Khí 5-Star Nổi Bật của banner sự kiện này.</t>
+          <t>Vũ Khí 5 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 5 Sao là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
+◇ Mỗi khi nhận được Vũ Khí 5 Sao, chắc chắn đó sẽ là Vũ Khí 5 Sao Nổi Bật của banner sự kiện này.</t>
         </is>
       </c>
     </row>
@@ -32026,9 +32026,9 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Resonators 5-Star
-◇ Tỷ lệ rơi cơ bản của Resonators 5-Star là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
-◇ Tất cả Resonators 5-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Resonator 5 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator 5 Sao là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
+◇ Tất cả Resonator 5 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32095,9 +32095,9 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Vũ Khí 5-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 5-Star là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
-◇ Mỗi khi nhận được Vũ Khí 5-Star, chắc chắn đó sẽ là Vũ Khí 5-Star Nổi Bật của banner sự kiện này.</t>
+          <t>Vũ Khí 5 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 5 Sao là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
+◇ Mỗi khi nhận được Vũ Khí 5 Sao, chắc chắn đó sẽ là Vũ Khí 5 Sao Nổi Bật của banner sự kiện này.</t>
         </is>
       </c>
     </row>
@@ -32164,9 +32164,9 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Resonators 5-Star
-◇ Tỷ lệ rơi cơ bản của Resonators 5-Star là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 2,40000%.
-◇ Tất cả Resonators 5-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Resonator 5 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator 5 Sao là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 2,40000%.
+◇ Tất cả Resonator 5 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32233,9 +32233,9 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Resonators 5-Star
-◇ Tỷ lệ rơi cơ bản của Resonators 5-Star là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
-◇ Mỗi khi nhận được Resonators 5-Star, chắc chắn đó sẽ là Resonators 5-Star Nổi Bật của banner sự kiện này.</t>
+          <t>Resonator 5 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator 5 Sao là 0,80000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 1,80000%.
+◇ Mỗi khi nhận được Resonator 5 Sao, chắc chắn đó sẽ là Resonator 5 Sao Nổi Bật của banner sự kiện này.</t>
         </is>
       </c>
     </row>
@@ -32302,9 +32302,9 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Resonators 5-Star
-◇ Tỷ lệ rơi cơ bản của Resonators 5-Star là 100%.
-◇ Mỗi khi nhận được Resonators 5-Star, chắc chắn đó sẽ là Resonators 5-Star Nổi Bật của banner sự kiện này.</t>
+          <t>Resonator 5 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator 5 Sao là 100%.
+◇ Mỗi khi nhận được Resonator 5 Sao, chắc chắn đó sẽ là Resonator 5 Sao Nổi Bật của banner sự kiện này.</t>
         </is>
       </c>
     </row>
@@ -32371,9 +32371,9 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Resonators &amp; Vũ Khí 4-Star
-◇ Tỷ lệ rơi cơ bản của Resonators hoặc Vũ Khí 4-Star là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
-◇ Mỗi khi nhận được vật phẩm 4-Star, có 50.00000% xác suất đó là Resonators 4-Star Nổi Bật của banner sự kiện này. Tất cả Resonators 4-Star Nổi Bật có tỷ lệ rơi như nhau; và 50.00000% xác suất là vật phẩm 4-Star không Nổi Bật ngẫu nhiên. Tất cả vật phẩm 4-Star không Nổi Bật có tỷ lệ rơi như nhau.</t>
+          <t>Resonator &amp; Vũ Khí 4 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator hoặc Vũ Khí 4 Sao là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
+◇ Mỗi khi nhận được vật phẩm 4 Sao, có 50.00000% xác suất đó là Resonator 4 Sao Nổi Bật của banner sự kiện này. Tất cả Resonator 4 Sao Nổi Bật có tỷ lệ rơi như nhau; và 50.00000% xác suất là vật phẩm 4 Sao không Nổi Bật ngẫu nhiên. Tất cả vật phẩm 4 Sao không Nổi Bật có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32440,9 +32440,9 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Resonators &amp; Vũ Khí 4-Star
-◇ Tỷ lệ rơi cơ bản của Resonators hoặc Vũ Khí 4-Star là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
-◇ Mỗi khi nhận được vật phẩm 4-Star, có 50.00000% xác suất đó là Resonators 4-Star Nổi Bật của banner sự kiện này. Tất cả Resonators 4-Star Nổi Bật có tỷ lệ rơi như nhau; và 50.00000% xác suất là vật phẩm 4-Star không Nổi Bật ngẫu nhiên. Tất cả vật phẩm 4-Star không Nổi Bật có tỷ lệ rơi như nhau.</t>
+          <t>Resonator &amp; Vũ Khí 4 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator hoặc Vũ Khí 4 Sao là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
+◇ Mỗi khi nhận được vật phẩm 4 Sao, có 50.00000% xác suất đó là Resonator 4 Sao Nổi Bật của banner sự kiện này. Tất cả Resonator 4 Sao Nổi Bật có tỷ lệ rơi như nhau; và 50.00000% xác suất là vật phẩm 4 Sao không Nổi Bật ngẫu nhiên. Tất cả vật phẩm 4 Sao không Nổi Bật có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32509,9 +32509,9 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Resonators &amp; Vũ Khí 4-Star
-◇ Tỷ lệ rơi cơ bản của Resonators hoặc Vũ Khí 4-Star là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
-◇ Tất cả vật phẩm 4-Star có tỷ lệ rơi như nhau.</t>
+          <t>Resonator &amp; Vũ Khí 4 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator hoặc Vũ Khí 4 Sao là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
+◇ Tất cả vật phẩm 4 Sao có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32578,9 +32578,9 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Resonators &amp; Vũ Khí 4-Star
-◇ Tỷ lệ rơi cơ bản của Resonators hoặc Vũ Khí 4-Star là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
-◇ Tất cả vật phẩm 4-Star có tỷ lệ rơi như nhau.</t>
+          <t>Resonator &amp; Vũ Khí 4 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator hoặc Vũ Khí 4 Sao là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
+◇ Tất cả vật phẩm 4 Sao có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32647,9 +32647,9 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Resonators &amp; Vũ Khí 4-Star
-◇ Tỷ lệ rơi cơ bản của Resonators hoặc Vũ Khí 4-Star là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 11.80000%.
-◇ Tất cả vật phẩm 4-Star có tỷ lệ rơi như nhau.</t>
+          <t>Resonator &amp; Vũ Khí 4 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator hoặc Vũ Khí 4 Sao là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 11.80000%.
+◇ Tất cả vật phẩm 4 Sao có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32716,9 +32716,9 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Resonators &amp; Vũ Khí 4-Star
-◇ Tỷ lệ rơi cơ bản của Resonators hoặc Vũ Khí 4-Star là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
-◇ Tất cả vật phẩm 4-Star có tỷ lệ rơi như nhau.</t>
+          <t>Resonator &amp; Vũ Khí 4 Sao
+◇ Tỷ lệ rơi cơ bản của Resonator hoặc Vũ Khí 4 Sao là 6.00000%. Tỷ lệ rơi trung bình (bao gồm cả Cơ Chế Bảo Đảm) là 12.00000%.
+◇ Tất cả vật phẩm 4 Sao có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32785,9 +32785,9 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Vũ Khí 3-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 3-Star là 93,20000%.
-◇ Tất cả Vũ Khí 3-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Vũ Khí 3 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 3 Sao là 93,20000%.
+◇ Tất cả Vũ Khí 3 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32854,9 +32854,9 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Vũ Khí 3-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 3-Star là 93,20000%.
-◇ Tất cả Vũ Khí 3-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Vũ Khí 3 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 3 Sao là 93,20000%.
+◇ Tất cả Vũ Khí 3 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32923,9 +32923,9 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Vũ Khí 3-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 3-Star là 93,20000%.
-◇ Tất cả Vũ Khí 3-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Vũ Khí 3 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 3 Sao là 93,20000%.
+◇ Tất cả Vũ Khí 3 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -32992,9 +32992,9 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Vũ Khí 3-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 3-Star là 93,20000%.
-◇ Tất cả Vũ Khí 3-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Vũ Khí 3 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 3 Sao là 93,20000%.
+◇ Tất cả Vũ Khí 3 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -33061,9 +33061,9 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Vũ Khí 3-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 3-Star là 93,20000%.
-◇ Tất cả Vũ Khí 3-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Vũ Khí 3 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 3 Sao là 93,20000%.
+◇ Tất cả Vũ Khí 3 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -33130,9 +33130,9 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Vũ Khí 3-Star
-◇ Tỷ lệ rơi cơ bản của Vũ Khí 3-Star là 93,20000%.
-◇ Tất cả Vũ Khí 3-Star đều có tỷ lệ rơi như nhau.</t>
+          <t>Vũ Khí 3 Sao
+◇ Tỷ lệ rơi cơ bản của Vũ Khí 3 Sao là 93,20000%.
+◇ Tất cả Vũ Khí 3 Sao đều có tỷ lệ rơi như nhau.</t>
         </is>
       </c>
     </row>
@@ -33265,7 +33265,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nó đã ghi lại thành công toàn bộ dữ liệu quan sát được trong Tacet Field HL-057. Sau khi ngoại suy và so sánh với mô hình dữ liệu lý thuyết, độ chính xác phù hợp dao động từ 0.8 đến 0.85, cho thấy độ chính xác cao.
+          <t xml:space="preserve">Nó đã ghi lại thành công toàn bộ dữ liệu quan sát được trong Tổ Tacet HL-057. Sau khi ngoại suy và so sánh với mô hình dữ liệu lý thuyết, độ chính xác phù hợp dao động từ 0.8 đến 0.85, cho thấy độ chính xác cao.
 </t>
         </is>
       </c>
@@ -33332,7 +33332,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đây là lần quan sát thứ ███ tại Tacet Field HL-057, do Máy Quan sát Tự động 11371A thực hiện.
+          <t xml:space="preserve">Đây là lần quan sát thứ ███ tại Tổ Tacet HL-057, do Máy Quan sát Tự động 11371A thực hiện.
 </t>
         </is>
       </c>
